--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487007_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487007_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.8933</v>
+        <v>4.7635</v>
       </c>
       <c r="E2" t="n">
-        <v>5.3695</v>
+        <v>2.5065</v>
       </c>
       <c r="F2" t="n">
-        <v>2.5238</v>
+        <v>2.257</v>
       </c>
       <c r="G2" t="n">
         <v>-0.7446</v>
@@ -610,13 +610,13 @@
         <v>1.4374</v>
       </c>
       <c r="S2" t="n">
-        <v>6.176</v>
+        <v>3.0462</v>
       </c>
       <c r="T2" t="n">
-        <v>4.1955</v>
+        <v>1.3325</v>
       </c>
       <c r="U2" t="n">
-        <v>1.9805</v>
+        <v>1.7137</v>
       </c>
       <c r="V2" t="n">
         <v>3.078</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.9741</v>
+        <v>3.8531</v>
       </c>
       <c r="E3" t="n">
-        <v>1.69</v>
+        <v>1.7172</v>
       </c>
       <c r="F3" t="n">
-        <v>2.2841</v>
+        <v>2.1359</v>
       </c>
       <c r="G3" t="n">
         <v>1.0889</v>
@@ -688,13 +688,13 @@
         <v>1.4374</v>
       </c>
       <c r="S3" t="n">
-        <v>1.5362</v>
+        <v>1.4151</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.1204</v>
+        <v>-0.09320000000000001</v>
       </c>
       <c r="U3" t="n">
-        <v>1.6566</v>
+        <v>1.5083</v>
       </c>
       <c r="V3" t="n">
         <v>0.9384</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.1533</v>
+        <v>3.3088</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.094</v>
+        <v>0.9133</v>
       </c>
       <c r="F4" t="n">
-        <v>2.2472</v>
+        <v>2.3955</v>
       </c>
       <c r="G4" t="n">
         <v>1.419</v>
@@ -766,13 +766,13 @@
         <v>1.6427</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.122</v>
+        <v>1.0335</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.1857</v>
+        <v>-0.1784</v>
       </c>
       <c r="U4" t="n">
-        <v>1.0637</v>
+        <v>1.2119</v>
       </c>
       <c r="V4" t="n">
         <v>0.2402</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.7969000000000001</v>
+        <v>1.2738</v>
       </c>
       <c r="E5" t="n">
-        <v>0.7022</v>
+        <v>1.357</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0946</v>
+        <v>-0.0832</v>
       </c>
       <c r="G5" t="n">
         <v>-1.7517</v>
@@ -844,13 +844,13 @@
         <v>0.8214</v>
       </c>
       <c r="S5" t="n">
-        <v>0.6369</v>
+        <v>1.1138</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.5542</v>
+        <v>0.1005</v>
       </c>
       <c r="U5" t="n">
-        <v>1.1911</v>
+        <v>1.0133</v>
       </c>
       <c r="V5" t="n">
         <v>2.117</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>P. ARRIBAS GOMEZ</t>
+          <t>M. ALVAREZ PUERTAS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.4316</v>
+        <v>-0.1045</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.1857</v>
+        <v>0.1742</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.2459</v>
+        <v>-0.2788</v>
       </c>
       <c r="G6" t="n">
-        <v>0.6227</v>
+        <v>0.6907</v>
       </c>
       <c r="H6" t="n">
-        <v>0.107</v>
+        <v>-0.6197</v>
       </c>
       <c r="I6" t="n">
-        <v>0.5157</v>
+        <v>1.3104</v>
       </c>
       <c r="J6" t="n">
-        <v>0.012</v>
+        <v>1.2824</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0779</v>
+        <v>0.0195</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.0659</v>
+        <v>1.2629</v>
       </c>
       <c r="M6" t="n">
-        <v>0.6107</v>
+        <v>-0.5917</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0291</v>
+        <v>-0.6392</v>
       </c>
       <c r="O6" t="n">
-        <v>0.5816</v>
+        <v>0.0475</v>
       </c>
       <c r="P6" t="n">
-        <v>0.8214</v>
+        <v>-0.8214</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-1.0267</v>
       </c>
       <c r="R6" t="n">
-        <v>0.8214</v>
+        <v>0.2053</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.1077</v>
+        <v>0.0261</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.1976</v>
+        <v>-0.0814</v>
       </c>
       <c r="U6" t="n">
-        <v>0.08989999999999999</v>
+        <v>0.1075</v>
       </c>
       <c r="V6" t="n">
-        <v>-1.7679</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.7679</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>M. ALVAREZ PUERTAS</t>
+          <t>P. ARRIBAS GOMEZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.5665</v>
+        <v>-0.2677</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.1396</v>
+        <v>-0.081</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.427</v>
+        <v>-0.1866</v>
       </c>
       <c r="G7" t="n">
-        <v>0.6907</v>
+        <v>0.6227</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.6197</v>
+        <v>0.107</v>
       </c>
       <c r="I7" t="n">
-        <v>1.3104</v>
+        <v>0.5157</v>
       </c>
       <c r="J7" t="n">
-        <v>1.2824</v>
+        <v>0.012</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0195</v>
+        <v>0.0779</v>
       </c>
       <c r="L7" t="n">
-        <v>1.2629</v>
+        <v>-0.0659</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.5917</v>
+        <v>0.6107</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.6392</v>
+        <v>0.0291</v>
       </c>
       <c r="O7" t="n">
-        <v>0.0475</v>
+        <v>0.5816</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.8214</v>
+        <v>0.8214</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.0267</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0.2053</v>
+        <v>0.8214</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.4359</v>
+        <v>0.0562</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.3952</v>
+        <v>-0.093</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.0407</v>
+        <v>0.1492</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>-1.7679</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-1.7679</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.19</v>
+        <v>-1.2723</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.89</v>
+        <v>-1.8241</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7</v>
+        <v>0.5518</v>
       </c>
       <c r="G8" t="n">
         <v>-0.9354</v>
@@ -1078,13 +1078,13 @@
         <v>0.4107</v>
       </c>
       <c r="S8" t="n">
-        <v>0.0329</v>
+        <v>-0.0494</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.5928</v>
+        <v>-0.527</v>
       </c>
       <c r="U8" t="n">
-        <v>0.6258</v>
+        <v>0.4776</v>
       </c>
       <c r="V8" t="n">
         <v>-0.6982</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.401</v>
+        <v>-1.3713</v>
       </c>
       <c r="E9" t="n">
         <v>-0.1976</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.2034</v>
+        <v>-1.1737</v>
       </c>
       <c r="G9" t="n">
         <v>-0.2498</v>
@@ -1156,13 +1156,13 @@
         <v>0.2053</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.1779</v>
+        <v>-0.1482</v>
       </c>
       <c r="T9" t="n">
         <v>-0.1976</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0198</v>
+        <v>0.0494</v>
       </c>
       <c r="V9" t="n">
         <v>-1.1786</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.1307</v>
+        <v>-2.1241</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.3007</v>
+        <v>-3.2348</v>
       </c>
       <c r="F10" t="n">
-        <v>1.17</v>
+        <v>1.1107</v>
       </c>
       <c r="G10" t="n">
         <v>-3.3116</v>
@@ -1234,13 +1234,13 @@
         <v>1.0267</v>
       </c>
       <c r="S10" t="n">
-        <v>0.7005</v>
+        <v>0.7071</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.6860000000000001</v>
+        <v>-0.6201</v>
       </c>
       <c r="U10" t="n">
-        <v>1.3865</v>
+        <v>1.3272</v>
       </c>
       <c r="V10" t="n">
         <v>0.4805</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.0396</v>
+        <v>-3.482</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.2188</v>
+        <v>-2.8391</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.8207</v>
+        <v>-0.6429</v>
       </c>
       <c r="G11" t="n">
         <v>-1.7826</v>
@@ -1312,13 +1312,13 @@
         <v>0.2053</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.606</v>
+        <v>-0.0485</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.8563</v>
+        <v>-0.4767</v>
       </c>
       <c r="U11" t="n">
-        <v>0.2503</v>
+        <v>0.4282</v>
       </c>
       <c r="V11" t="n">
         <v>-0.8295</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-6.6702</v>
+        <v>-5.5303</v>
       </c>
       <c r="E12" t="n">
-        <v>-6.4801</v>
+        <v>-5.5774</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.1901</v>
+        <v>0.0471</v>
       </c>
       <c r="G12" t="n">
         <v>-4.0959</v>
@@ -1390,13 +1390,13 @@
         <v>1.0267</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.3689</v>
+        <v>0.7709</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.2516</v>
+        <v>-0.3489</v>
       </c>
       <c r="U12" t="n">
-        <v>0.8827</v>
+        <v>1.1198</v>
       </c>
       <c r="V12" t="n">
         <v>-1.1786</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-1.612000000000001</v>
+        <v>-0.9530000000000003</v>
       </c>
       <c r="E13" t="n">
-        <v>-7.744800000000001</v>
+        <v>-7.0858</v>
       </c>
       <c r="F13" t="n">
-        <v>6.132599999999999</v>
+        <v>6.1328</v>
       </c>
       <c r="G13" t="n">
         <v>-9.0503</v>
@@ -1468,13 +1468,13 @@
         <v>9.2403</v>
       </c>
       <c r="S13" t="n">
-        <v>7.264100000000001</v>
+        <v>7.922799999999999</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.8419</v>
+        <v>-1.1833</v>
       </c>
       <c r="U13" t="n">
-        <v>9.106199999999999</v>
+        <v>9.1061</v>
       </c>
       <c r="V13" t="n">
         <v>1.2013</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>8.9331</v>
+        <v>8.3123</v>
       </c>
       <c r="E14" t="n">
-        <v>5.576</v>
+        <v>5.7852</v>
       </c>
       <c r="F14" t="n">
-        <v>3.3571</v>
+        <v>2.5271</v>
       </c>
       <c r="G14" t="n">
         <v>6.5993</v>
@@ -1546,13 +1546,13 @@
         <v>1.6427</v>
       </c>
       <c r="S14" t="n">
-        <v>0.1017</v>
+        <v>-0.5191</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.4492</v>
+        <v>-1.24</v>
       </c>
       <c r="U14" t="n">
-        <v>1.5509</v>
+        <v>0.7209</v>
       </c>
       <c r="V14" t="n">
         <v>0.5893</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.7677</v>
+        <v>1.6369</v>
       </c>
       <c r="E15" t="n">
-        <v>0.4087</v>
+        <v>0.7225</v>
       </c>
       <c r="F15" t="n">
-        <v>1.359</v>
+        <v>0.9144</v>
       </c>
       <c r="G15" t="n">
         <v>0.7227</v>
@@ -1624,13 +1624,13 @@
         <v>1.2321</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.8852</v>
+        <v>-1.016</v>
       </c>
       <c r="T15" t="n">
-        <v>-1.5809</v>
+        <v>-1.2671</v>
       </c>
       <c r="U15" t="n">
-        <v>0.6957</v>
+        <v>0.2511</v>
       </c>
       <c r="V15" t="n">
         <v>0.6982</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.1533</v>
+        <v>0.6912</v>
       </c>
       <c r="E16" t="n">
-        <v>1.4335</v>
+        <v>1.1197</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.2803</v>
+        <v>-0.4285</v>
       </c>
       <c r="G16" t="n">
         <v>1.5155</v>
@@ -1702,13 +1702,13 @@
         <v>1.2321</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.3273</v>
+        <v>-0.7893</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.3566</v>
+        <v>-0.6704</v>
       </c>
       <c r="U16" t="n">
-        <v>0.0293</v>
+        <v>-0.1189</v>
       </c>
       <c r="V16" t="n">
         <v>-0.2402</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>O. BRAMBLE</t>
+          <t>M. VORONIN</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.2111</v>
+        <v>0.6252</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.0017</v>
+        <v>-0.9365</v>
       </c>
       <c r="F17" t="n">
-        <v>1.2128</v>
+        <v>1.5618</v>
       </c>
       <c r="G17" t="n">
-        <v>0.6493</v>
+        <v>1.6883</v>
       </c>
       <c r="H17" t="n">
-        <v>1.3754</v>
+        <v>2.7539</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.7261</v>
+        <v>-1.0656</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.343</v>
+        <v>1.5428</v>
       </c>
       <c r="K17" t="n">
-        <v>0.3149</v>
+        <v>1.6351</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.6579</v>
+        <v>-0.09229999999999999</v>
       </c>
       <c r="M17" t="n">
-        <v>0.9923999999999999</v>
+        <v>0.1455</v>
       </c>
       <c r="N17" t="n">
-        <v>1.0606</v>
+        <v>1.1188</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.0682</v>
+        <v>-0.9732</v>
       </c>
       <c r="P17" t="n">
-        <v>1.2321</v>
+        <v>-0.8214</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-2.0534</v>
       </c>
       <c r="R17" t="n">
         <v>1.2321</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.7094</v>
+        <v>-0.831</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.6587</v>
+        <v>-1.0152</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.0507</v>
+        <v>0.1842</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.9609</v>
+        <v>0.5893</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>0.5893</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.9609</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>J. GONZALEZ ALBADALEJO</t>
+          <t>O. BRAMBLE</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.0241</v>
+        <v>0.5825</v>
       </c>
       <c r="E18" t="n">
-        <v>-2.5741</v>
+        <v>-0.8971</v>
       </c>
       <c r="F18" t="n">
-        <v>2.5982</v>
+        <v>1.4796</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.2232</v>
+        <v>0.6493</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.1102</v>
+        <v>1.3754</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.113</v>
+        <v>-0.7261</v>
       </c>
       <c r="J18" t="n">
-        <v>-2.0607</v>
+        <v>-0.343</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.7844</v>
+        <v>0.3149</v>
       </c>
       <c r="L18" t="n">
-        <v>-1.2763</v>
+        <v>-0.6579</v>
       </c>
       <c r="M18" t="n">
-        <v>1.8375</v>
+        <v>0.9923999999999999</v>
       </c>
       <c r="N18" t="n">
-        <v>0.6743</v>
+        <v>1.0606</v>
       </c>
       <c r="O18" t="n">
-        <v>1.1633</v>
+        <v>-0.0682</v>
       </c>
       <c r="P18" t="n">
-        <v>-1.6427</v>
+        <v>1.2321</v>
       </c>
       <c r="Q18" t="n">
-        <v>-3.0801</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.4374</v>
+        <v>1.2321</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.2968</v>
+        <v>-0.338</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.6201</v>
+        <v>-0.5541</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.6767</v>
+        <v>0.2161</v>
       </c>
       <c r="V18" t="n">
-        <v>3.1868</v>
+        <v>-0.9609</v>
       </c>
       <c r="W18" t="n">
-        <v>3.1868</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-0.9609</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>M. VORONIN</t>
+          <t>J. GONZALEZ ALBADALEJO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,64 +1891,64 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.0129</v>
+        <v>0.0956</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.0411</v>
+        <v>-2.888</v>
       </c>
       <c r="F19" t="n">
-        <v>1.0282</v>
+        <v>2.9836</v>
       </c>
       <c r="G19" t="n">
-        <v>1.6883</v>
+        <v>-0.2232</v>
       </c>
       <c r="H19" t="n">
-        <v>2.7539</v>
+        <v>-0.1102</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.0656</v>
+        <v>-0.113</v>
       </c>
       <c r="J19" t="n">
-        <v>1.5428</v>
+        <v>-2.0607</v>
       </c>
       <c r="K19" t="n">
-        <v>1.6351</v>
+        <v>-0.7844</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.09229999999999999</v>
+        <v>-1.2763</v>
       </c>
       <c r="M19" t="n">
-        <v>0.1455</v>
+        <v>1.8375</v>
       </c>
       <c r="N19" t="n">
-        <v>1.1188</v>
+        <v>0.6743</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.9732</v>
+        <v>1.1633</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.8214</v>
+        <v>-1.6427</v>
       </c>
       <c r="Q19" t="n">
-        <v>-2.0534</v>
+        <v>-3.0801</v>
       </c>
       <c r="R19" t="n">
-        <v>1.2321</v>
+        <v>1.4374</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.4692</v>
+        <v>-1.2252</v>
       </c>
       <c r="T19" t="n">
-        <v>-1.1198</v>
+        <v>-0.9339</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.3494</v>
+        <v>-0.2913</v>
       </c>
       <c r="V19" t="n">
-        <v>0.5893</v>
+        <v>3.1868</v>
       </c>
       <c r="W19" t="n">
-        <v>0.5893</v>
+        <v>3.1868</v>
       </c>
       <c r="X19" t="n">
         <v>0</v>
@@ -1969,10 +1969,10 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.8129</v>
+        <v>-1.7083</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.7709</v>
+        <v>-1.6663</v>
       </c>
       <c r="F20" t="n">
         <v>-0.042</v>
@@ -2014,10 +2014,10 @@
         <v>0.2053</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.3952</v>
+        <v>-0.2906</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.7246</v>
+        <v>-0.62</v>
       </c>
       <c r="U20" t="n">
         <v>0.3294</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.6086</v>
+        <v>-2.4603</v>
       </c>
       <c r="E21" t="n">
         <v>-1.3116</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.297</v>
+        <v>-1.1488</v>
       </c>
       <c r="G21" t="n">
         <v>0.8475</v>
@@ -2092,13 +2092,13 @@
         <v>0.4107</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.9202</v>
+        <v>-0.772</v>
       </c>
       <c r="T21" t="n">
         <v>-0.7905</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.1297</v>
+        <v>0.0185</v>
       </c>
       <c r="V21" t="n">
         <v>-2.9466</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.9602</v>
+        <v>-2.8294</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.7868000000000001</v>
+        <v>-1.1006</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.1734</v>
+        <v>-1.7288</v>
       </c>
       <c r="G22" t="n">
         <v>0.3131</v>
@@ -2170,13 +2170,13 @@
         <v>0.8214</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.3</v>
+        <v>-1.1691</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.6860000000000001</v>
+        <v>-0.9998</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.614</v>
+        <v>-0.1694</v>
       </c>
       <c r="V22" t="n">
         <v>-1.7679</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.0828</v>
+        <v>-3.3339</v>
       </c>
       <c r="E23" t="n">
-        <v>-5.0646</v>
+        <v>-4.96</v>
       </c>
       <c r="F23" t="n">
-        <v>1.9818</v>
+        <v>1.6261</v>
       </c>
       <c r="G23" t="n">
         <v>-2.7059</v>
@@ -2248,13 +2248,13 @@
         <v>0.8214</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.06270000000000001</v>
+        <v>-0.3138</v>
       </c>
       <c r="T23" t="n">
-        <v>-1.1198</v>
+        <v>-1.0152</v>
       </c>
       <c r="U23" t="n">
-        <v>1.0571</v>
+        <v>0.7014</v>
       </c>
       <c r="V23" t="n">
         <v>-0.1088</v>
@@ -2281,19 +2281,19 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>1.611899999999999</v>
+        <v>1.611800000000002</v>
       </c>
       <c r="E24" t="n">
-        <v>-6.1326</v>
+        <v>-6.1327</v>
       </c>
       <c r="F24" t="n">
-        <v>7.7444</v>
+        <v>7.7445</v>
       </c>
       <c r="G24" t="n">
         <v>9.050500000000001</v>
       </c>
       <c r="H24" t="n">
-        <v>9.747700000000002</v>
+        <v>9.7477</v>
       </c>
       <c r="I24" t="n">
         <v>-0.6973</v>
@@ -2308,7 +2308,7 @@
         <v>-4.1995</v>
       </c>
       <c r="M24" t="n">
-        <v>4.5202</v>
+        <v>4.520200000000001</v>
       </c>
       <c r="N24" t="n">
         <v>1.0184</v>
@@ -2326,16 +2326,16 @@
         <v>10.2673</v>
       </c>
       <c r="S24" t="n">
-        <v>-7.2643</v>
+        <v>-7.2641</v>
       </c>
       <c r="T24" t="n">
-        <v>-9.106199999999999</v>
+        <v>-9.106200000000001</v>
       </c>
       <c r="U24" t="n">
-        <v>1.8419</v>
+        <v>1.842</v>
       </c>
       <c r="V24" t="n">
-        <v>-1.201</v>
+        <v>-1.201000000000001</v>
       </c>
       <c r="W24" t="n">
         <v>7.6835</v>
